--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B15314-9EC1-4780-AF3E-8E285D82EE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BABC58-84CC-4EAA-88E5-A1D40482158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -257,9 +257,6 @@
     <t>Opportunities</t>
   </si>
   <si>
-    <t>Eric Winthrop</t>
-  </si>
-  <si>
     <t>Derek Janisch</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+  </si>
+  <si>
+    <t>James Craven</t>
   </si>
 </sst>
 </file>
@@ -738,7 +738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1064,35 +1064,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s">
         <v>16</v>
@@ -1297,13 +1297,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1311,12 +1311,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1327,14 +1327,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A88144-1ABB-4FDF-9E95-9A1D88FAECE2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1347,17 +1347,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD21A9F-3A38-4273-AC4A-B76AE5603A76}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1370,20 +1370,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.88671875" customWidth="1"/>
-    <col min="10" max="10" width="31.5546875" customWidth="1"/>
-    <col min="11" max="11" width="51.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.85546875" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" customWidth="1"/>
+    <col min="11" max="11" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>36</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>55</v>
       </c>
@@ -1462,128 +1462,128 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94339ED7-FD87-4B3E-A3E9-88C21A2B49CE}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="121.44140625" customWidth="1"/>
-    <col min="3" max="3" width="123.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="121.42578125" customWidth="1"/>
+    <col min="3" max="3" width="123.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BABC58-84CC-4EAA-88E5-A1D40482158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86D5C0D-739A-4DDC-A5A6-427047BCA688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -1115,177 +1115,177 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
       <c r="Z2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AD2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1305,18 +1305,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1331,12 +1331,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1354,12 +1354,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1385,72 +1385,72 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="C1" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="H1" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1470,120 +1470,120 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86D5C0D-739A-4DDC-A5A6-427047BCA688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357C0D54-A244-4CEC-9041-A3ADF4E5F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -332,10 +332,10 @@
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
   <si>
-    <t>James Craven</t>
-  </si>
-  <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1201,7 @@
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357C0D54-A244-4CEC-9041-A3ADF4E5F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9D50F5-DD4B-472F-9232-0684B170F871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -329,13 +329,13 @@
     <t>Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
-  </si>
-  <si>
     <t>Business Services</t>
   </si>
   <si>
     <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1201,7 @@
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
@@ -1473,9 +1473,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9D50F5-DD4B-472F-9232-0684B170F871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0499D60A-F8E5-40C4-A0A0-1686EC45EF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -329,13 +326,16 @@
     <t>Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Eric Winthrop</t>
   </si>
   <si>
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
   </si>
 </sst>
 </file>
@@ -1064,35 +1064,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1103,189 +1103,189 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="V2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X2" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Y2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" t="s">
         <v>42</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC2" t="s">
         <v>63</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="AD2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" t="s">
-        <v>58</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>8</v>
-      </c>
       <c r="AE2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1297,26 +1297,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1327,16 +1327,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A88144-1ABB-4FDF-9E95-9A1D88FAECE2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1347,19 +1347,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD21A9F-3A38-4273-AC4A-B76AE5603A76}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1370,87 +1370,87 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.85546875" customWidth="1"/>
-    <col min="10" max="10" width="31.5703125" customWidth="1"/>
-    <col min="11" max="11" width="51.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.88671875" customWidth="1"/>
+    <col min="10" max="10" width="31.5546875" customWidth="1"/>
+    <col min="11" max="11" width="51.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="H1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="270" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1462,128 +1462,128 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94339ED7-FD87-4B3E-A3E9-88C21A2B49CE}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="121.42578125" customWidth="1"/>
-    <col min="3" max="3" width="123.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="121.44140625" customWidth="1"/>
+    <col min="3" max="3" width="123.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0499D60A-F8E5-40C4-A0A0-1686EC45EF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3155797-66F7-4141-BDE6-FAD4FA2FB45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -332,10 +332,10 @@
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -1064,35 +1064,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1190,7 +1190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1297,13 +1297,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -1327,14 +1327,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A88144-1ABB-4FDF-9E95-9A1D88FAECE2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1347,17 +1347,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD21A9F-3A38-4273-AC4A-B76AE5603A76}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1370,20 +1370,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.88671875" customWidth="1"/>
-    <col min="10" max="10" width="31.5546875" customWidth="1"/>
-    <col min="11" max="11" width="51.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.85546875" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" customWidth="1"/>
+    <col min="11" max="11" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>34</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>53</v>
       </c>
@@ -1462,18 +1462,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94339ED7-FD87-4B3E-A3E9-88C21A2B49CE}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="121.44140625" customWidth="1"/>
-    <col min="3" max="3" width="123.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="121.42578125" customWidth="1"/>
+    <col min="3" max="3" width="123.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>99</v>
       </c>
@@ -1481,107 +1481,107 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>96</v>
       </c>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDF7A19-0568-4B48-8B9C-F91BAA1E3CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A903E907-AE3F-4B1C-8672-4024EFD20B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -329,13 +329,13 @@
     <t>Eric Winthrop</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Service Benefit was provided is required.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1176,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1274,7 +1274,7 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A903E907-AE3F-4B1C-8672-4024EFD20B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F185C44-A3C2-4841-8DD0-C48B96C283E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Service Benefit was provided is required.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Service Benefit was provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F185C44-A3C2-4841-8DD0-C48B96C283E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C22A130-4367-4EF9-B4BC-F42917D8025B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Service Benefit was provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
@@ -1064,13 +1064,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -1094,14 +1094,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A88144-1ABB-4FDF-9E95-9A1D88FAECE2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1114,17 +1114,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD21A9F-3A38-4273-AC4A-B76AE5603A76}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1137,35 +1137,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1370,20 +1370,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.85546875" customWidth="1"/>
-    <col min="10" max="10" width="31.5703125" customWidth="1"/>
-    <col min="11" max="11" width="51.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.88671875" customWidth="1"/>
+    <col min="10" max="10" width="31.5546875" customWidth="1"/>
+    <col min="11" max="11" width="51.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>34</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="270" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>53</v>
       </c>
@@ -1462,18 +1462,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94339ED7-FD87-4B3E-A3E9-88C21A2B49CE}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="121.42578125" customWidth="1"/>
-    <col min="3" max="3" width="123.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="121.44140625" customWidth="1"/>
+    <col min="3" max="3" width="123.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>101</v>
       </c>
@@ -1481,107 +1481,107 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>96</v>
       </c>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C22A130-4367-4EF9-B4BC-F42917D8025B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912CF9F8-565E-4BAE-9D23-452045AAB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -335,7 +335,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.KYC/Client/Subject/Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
@@ -1064,13 +1064,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -1094,14 +1094,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A88144-1ABB-4FDF-9E95-9A1D88FAECE2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1114,17 +1114,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD21A9F-3A38-4273-AC4A-B76AE5603A76}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1137,35 +1137,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1370,20 +1370,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.88671875" customWidth="1"/>
-    <col min="10" max="10" width="31.5546875" customWidth="1"/>
-    <col min="11" max="11" width="51.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.85546875" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" customWidth="1"/>
+    <col min="11" max="11" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>34</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>53</v>
       </c>
@@ -1462,18 +1462,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94339ED7-FD87-4B3E-A3E9-88C21A2B49CE}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="121.44140625" customWidth="1"/>
-    <col min="3" max="3" width="123.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="121.42578125" customWidth="1"/>
+    <col min="3" max="3" width="123.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>101</v>
       </c>
@@ -1481,107 +1481,107 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>96</v>
       </c>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912CF9F8-565E-4BAE-9D23-452045AAB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073E3083-A233-4BB3-A410-4B52D200F33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -335,7 +335,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.KYC/Client/Subject/Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.KYC/Client/Subject/Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.KYC/Client/Subject/Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073E3083-A233-4BB3-A410-4B52D200F33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D580C4-E1E2-40CF-B15A-4DF8A22E0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
+++ b/TestData/LV_T1693_ValidationsToBeCompletedBeforeFROpportunityIsApproved.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D580C4-E1E2-40CF-B15A-4DF8A22E0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BDE4998-7C8E-4EB1-AAC0-D9EB3745C4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.KYC/Client/Subject/Referral--&gt;Referral Info: Referral Type is required.Client/Subject &amp; Referral--&gt;Referral Info: Legal Advisor to Company is required.KYC/Client/Subject/Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Marketing--&gt;Information: Client Description is required.Marketing--&gt;Information: Select \"Total Debt(MM) Confirmed\" checkbox to confirm Total Debt is most up to date.Marketing--&gt;Information: Total Debt HL represents(MM), input zero if not applicable.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.KYC/Client/Subject/Referral--&gt;Referral Info: Referral Type is required.KYC/Client/Subject/Referral--&gt;Referral Info: Legal Advisor to Company is required.KYC/Client/Subject/Referral--&gt;Referral Info: Legal Advisor to HL Client Group is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: Estimated Close Date is required.Pitches/Mandate Awards: A Pitch/Mandate's Outcome is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
